--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,468 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131363419</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91838</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västervik Böljerum 3:63, Verkbäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>591670</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6399715</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera talltickor på en tall</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Blandad skog med gamla tallar, ekar, aspar samt ett litet område med alar (vissa med socklar).</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131429756</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101224</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västervik Böljerum 3:63, Verkbäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>591777</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6399658</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131429716</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91838</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västervik Böljerum 3:63, Verkbäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>591788</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6399710</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131429788</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101224</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västervik Böljerum 3:63, Verkbäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>591694</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6399704</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>131363419</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131429756</v>
       </c>
       <c r="B4" t="n">
-        <v>101224</v>
+        <v>101225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131429716</v>
       </c>
       <c r="B5" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131429788</v>
       </c>
       <c r="B6" t="n">
-        <v>101224</v>
+        <v>101225</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>131363419</v>
       </c>
       <c r="B3" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131429756</v>
       </c>
       <c r="B4" t="n">
-        <v>101225</v>
+        <v>101228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131429716</v>
       </c>
       <c r="B5" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131429788</v>
       </c>
       <c r="B6" t="n">
-        <v>101225</v>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>131363419</v>
       </c>
       <c r="B3" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131429756</v>
       </c>
       <c r="B4" t="n">
-        <v>101228</v>
+        <v>101231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131429716</v>
       </c>
       <c r="B5" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131429788</v>
       </c>
       <c r="B6" t="n">
-        <v>101228</v>
+        <v>101231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>131363419</v>
       </c>
       <c r="B3" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131429756</v>
       </c>
       <c r="B4" t="n">
-        <v>101231</v>
+        <v>101237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131429716</v>
       </c>
       <c r="B5" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131429788</v>
       </c>
       <c r="B6" t="n">
-        <v>101231</v>
+        <v>101237</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>131429756</v>
       </c>
       <c r="B4" t="n">
-        <v>101237</v>
+        <v>101238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131429788</v>
       </c>
       <c r="B6" t="n">
-        <v>101237</v>
+        <v>101238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>131363419</v>
       </c>
       <c r="B3" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131429756</v>
       </c>
       <c r="B4" t="n">
-        <v>101238</v>
+        <v>101239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131429716</v>
       </c>
       <c r="B5" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131429788</v>
       </c>
       <c r="B6" t="n">
-        <v>101238</v>
+        <v>101239</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>131363419</v>
       </c>
       <c r="B3" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131429756</v>
       </c>
       <c r="B4" t="n">
-        <v>101239</v>
+        <v>101242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131429716</v>
       </c>
       <c r="B5" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131429788</v>
       </c>
       <c r="B6" t="n">
-        <v>101239</v>
+        <v>101242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>131429756</v>
       </c>
       <c r="B4" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131429788</v>
       </c>
       <c r="B6" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1246,6 +1246,326 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131905526</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91854</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 9952, Verkebäcksviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>591801</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6399700</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131905554</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57900</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 9952, Verkebäcksviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>591848</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6399674</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökt i död ganska klen tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131906135</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58584</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 9952, Verkebäcksviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>591745</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6399683</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>131363419</v>
       </c>
       <c r="B3" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131429756</v>
       </c>
       <c r="B4" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131429716</v>
       </c>
       <c r="B5" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131429788</v>
       </c>
       <c r="B6" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>131905526</v>
       </c>
       <c r="B7" t="n">
-        <v>91854</v>
+        <v>91859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131905554</v>
       </c>
       <c r="B8" t="n">
-        <v>57900</v>
+        <v>57901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>131906135</v>
       </c>
       <c r="B9" t="n">
-        <v>58584</v>
+        <v>58585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -1251,7 +1251,7 @@
         <v>131905526</v>
       </c>
       <c r="B7" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>131906135</v>
       </c>
       <c r="B9" t="n">
-        <v>58629</v>
+        <v>58631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -1251,7 +1251,7 @@
         <v>131905526</v>
       </c>
       <c r="B7" t="n">
-        <v>91913</v>
+        <v>91919</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131905554</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>131906135</v>
       </c>
       <c r="B9" t="n">
-        <v>58631</v>
+        <v>58632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 9952-2026 artfynd.xlsx
+++ b/artfynd/A 9952-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74977104</v>
+        <v>131363419</v>
       </c>
       <c r="B2" t="n">
-        <v>110806</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219716</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>24 Arabien 350 m O, Sm</t>
+          <t>Västervik Böljerum 3:63, Verkbäck, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591680</v>
+        <v>591670</v>
       </c>
       <c r="R2" t="n">
-        <v>6399726</v>
+        <v>6399715</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +751,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1981-01-01</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1985-12-31</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G0i 0837. SOM: Selinum carvifolia. LEG: Birger Danielsson</t>
+          <t>Flera talltickor på en tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,37 +780,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skogsäng</t>
+          <t>Blandad skog med gamla tallar, ekar, aspar samt ett litet område med alar (vissa med socklar).</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131363419</v>
+        <v>131429603</v>
       </c>
       <c r="B3" t="n">
-        <v>91867</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -828,14 +846,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västervik Böljerum 3:63, Verkbäck, Sm</t>
+          <t>Västervik Böljerum 3:36, Verkebäck, Verkbäck, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591670</v>
+        <v>591659</v>
       </c>
       <c r="R3" t="n">
-        <v>6399715</v>
+        <v>6399680</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,27 +880,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera talltickor på en tall</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,11 +907,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandad skog med gamla tallar, ekar, aspar samt ett litet område med alar (vissa med socklar).</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -915,38 +923,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131429756</v>
+        <v>131429716</v>
       </c>
       <c r="B4" t="n">
-        <v>101257</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591777</v>
+        <v>591788</v>
       </c>
       <c r="R4" t="n">
-        <v>6399658</v>
+        <v>6399710</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,19 +1002,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131429716</v>
+        <v>131905526</v>
       </c>
       <c r="B5" t="n">
-        <v>91867</v>
+        <v>91995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,17 +1074,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västervik Böljerum 3:63, Verkbäck, Sm</t>
+          <t>A 9952, Verkebäcksviken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591788</v>
+        <v>591801</v>
       </c>
       <c r="R5" t="n">
-        <v>6399710</v>
+        <v>6399700</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,12 +1108,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,22 +1129,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131429788</v>
+        <v>131905554</v>
       </c>
       <c r="B6" t="n">
-        <v>101257</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,41 +1152,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västervik Böljerum 3:63, Verkbäck, Sm</t>
+          <t>A 9952, Verkebäcksviken, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591694</v>
+        <v>591848</v>
       </c>
       <c r="R6" t="n">
-        <v>6399704</v>
+        <v>6399674</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,22 +1214,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökt i död ganska klen tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,51 +1233,50 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131905526</v>
+        <v>131728034</v>
       </c>
       <c r="B7" t="n">
-        <v>91919</v>
+        <v>58250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>103019</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1281,26 +1284,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 9952, Verkebäcksviken, Sm</t>
+          <t>Västervik Böljrerum 3:63, Verkbäck, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591801</v>
+        <v>591748</v>
       </c>
       <c r="R7" t="n">
-        <v>6399700</v>
+        <v>6399757</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,12 +1332,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,29 +1356,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131905554</v>
+        <v>131429831</v>
       </c>
       <c r="B8" t="n">
-        <v>57946</v>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,16 +1385,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1385,28 +1402,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 9952, Verkebäcksviken, Sm</t>
+          <t>Västervik Böljerum 3:63, Verkbäck, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591848</v>
+        <v>591667</v>
       </c>
       <c r="R8" t="n">
-        <v>6399674</v>
+        <v>6399601</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,17 +1451,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökt i död ganska klen tall</t>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,12 +1481,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1470,7 +1496,7 @@
         <v>131906135</v>
       </c>
       <c r="B9" t="n">
-        <v>58632</v>
+        <v>58658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,6 +1592,469 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>74977104</v>
+      </c>
+      <c r="B10" t="n">
+        <v>111398</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219716</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Krusfrö</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Selinum carvifolia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>24 Arabien 350 m O, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>591680</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6399726</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1981-01-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1985-12-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G0i 0837. SOM: Selinum carvifolia. LEG: Birger Danielsson</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Skogsäng</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131429756</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västervik Böljerum 3:63, Verkbäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>591777</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6399658</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131429788</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västervik Böljerum 3:63, Verkbäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>591694</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6399704</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131728016</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Västervik Böljerum 3:63, Verkbäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>591644</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6399635</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
